--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="63.109375" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,28 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Vi Xuan Cu</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10:23:13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
